--- a/owlcms/src/main/resources/templates/credentials/Athletes_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Athletes_A4.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\cards\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E76F6972-B101-46F9-B4B1-58CD96BED0E0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B06AED-3D01-4E4C-BBAD-29BAC89AF153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -177,7 +177,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
   <si>
     <t>${athlete.fixedName}</t>
   </si>
@@ -209,6 +209,9 @@
   <si>
     <t>${a.custom1} ${a.custom2}</t>
   </si>
+  <si>
+    <t>ATHLETE</t>
+  </si>
 </sst>
 </file>
 
@@ -217,7 +220,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]d\-mmm\-yy;@"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -312,8 +315,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -326,6 +337,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="22">
     <border>
@@ -562,7 +579,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="55">
+  <cellXfs count="52">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -617,6 +634,21 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -629,69 +661,49 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="10" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1063,13 +1075,13 @@
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" ht="58.5" customHeight="1" x14ac:dyDescent="0.35">
       <c r="B3" s="9"/>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="34" t="s">
         <v>1</v>
       </c>
-      <c r="D3" s="29"/>
-      <c r="E3" s="29"/>
-      <c r="F3" s="29"/>
-      <c r="G3" s="29"/>
+      <c r="D3" s="34"/>
+      <c r="E3" s="34"/>
+      <c r="F3" s="34"/>
+      <c r="G3" s="34"/>
       <c r="H3" s="10"/>
     </row>
     <row r="4" spans="1:9" ht="6" customHeight="1" x14ac:dyDescent="0.25">
@@ -1081,16 +1093,16 @@
       <c r="G4" s="12"/>
       <c r="H4" s="13"/>
     </row>
-    <row r="5" spans="1:9" s="14" customFormat="1" ht="6" customHeight="1" x14ac:dyDescent="0.5">
+    <row r="5" spans="1:9" s="14" customFormat="1" ht="3" customHeight="1" x14ac:dyDescent="0.5">
       <c r="B5" s="15"/>
-      <c r="C5" s="33"/>
-      <c r="D5" s="33"/>
-      <c r="E5" s="33"/>
-      <c r="F5" s="33"/>
-      <c r="G5" s="33"/>
+      <c r="C5" s="40"/>
+      <c r="D5" s="40"/>
+      <c r="E5" s="40"/>
+      <c r="F5" s="40"/>
+      <c r="G5" s="40"/>
       <c r="H5" s="16"/>
     </row>
-    <row r="6" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:9" ht="4.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="11"/>
       <c r="C6" s="12"/>
       <c r="D6" s="12"/>
@@ -1099,57 +1111,59 @@
       <c r="G6" s="12"/>
       <c r="H6" s="13"/>
     </row>
-    <row r="7" spans="1:9" s="49" customFormat="1" ht="51" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B7" s="50"/>
-      <c r="C7" s="48" t="s">
+    <row r="7" spans="1:9" s="30" customFormat="1" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B7" s="31"/>
+      <c r="C7" s="41" t="s">
         <v>0</v>
       </c>
-      <c r="D7" s="48"/>
-      <c r="E7" s="48"/>
-      <c r="F7" s="48"/>
-      <c r="G7" s="48"/>
-      <c r="H7" s="51"/>
-    </row>
-    <row r="8" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
+      <c r="F7" s="41"/>
+      <c r="G7" s="41"/>
+      <c r="H7" s="32"/>
+    </row>
+    <row r="8" spans="1:9" ht="39.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="11"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="32"/>
-      <c r="F8" s="32"/>
-      <c r="G8" s="32"/>
+      <c r="C8" s="42" t="s">
+        <v>10</v>
+      </c>
+      <c r="D8" s="42"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="42"/>
+      <c r="G8" s="42"/>
       <c r="H8" s="13"/>
     </row>
-    <row r="9" spans="1:9" ht="7.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:9" ht="6.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="11"/>
       <c r="E9" s="17"/>
       <c r="G9" s="17"/>
       <c r="H9" s="13"/>
     </row>
-    <row r="10" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B10" s="28"/>
-      <c r="E10" s="34"/>
-      <c r="F10" s="35"/>
-      <c r="G10" s="36"/>
+    <row r="10" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B10" s="33"/>
+      <c r="E10" s="43"/>
+      <c r="F10" s="44"/>
+      <c r="G10" s="45"/>
       <c r="H10" s="13"/>
     </row>
-    <row r="11" spans="1:9" ht="101.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B11" s="28"/>
+    <row r="11" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B11" s="33"/>
       <c r="C11" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="E11" s="37"/>
-      <c r="F11" s="38"/>
-      <c r="G11" s="39"/>
+      <c r="E11" s="46"/>
+      <c r="F11" s="47"/>
+      <c r="G11" s="48"/>
       <c r="H11" s="13"/>
     </row>
-    <row r="12" spans="1:9" ht="102.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B12" s="28"/>
+    <row r="12" spans="1:9" ht="87" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B12" s="33"/>
       <c r="C12" s="19" t="s">
         <v>3</v>
       </c>
-      <c r="E12" s="40"/>
-      <c r="F12" s="41"/>
-      <c r="G12" s="42"/>
+      <c r="E12" s="49"/>
+      <c r="F12" s="50"/>
+      <c r="G12" s="51"/>
       <c r="H12" s="13"/>
     </row>
     <row r="13" spans="1:9" ht="18" customHeight="1" x14ac:dyDescent="0.25">
@@ -1160,35 +1174,32 @@
     </row>
     <row r="14" spans="1:9" s="21" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B14" s="22"/>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="D14" s="31"/>
-      <c r="E14" s="31"/>
-      <c r="F14" s="31"/>
-      <c r="G14" s="31"/>
+      <c r="D14" s="36"/>
+      <c r="E14" s="36"/>
+      <c r="F14" s="36"/>
+      <c r="G14" s="36"/>
       <c r="H14" s="23"/>
     </row>
     <row r="15" spans="1:9" s="21" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B15" s="22"/>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="36" t="s">
         <v>9</v>
       </c>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
-      <c r="G15" s="31"/>
+      <c r="D15" s="36"/>
+      <c r="E15" s="36"/>
+      <c r="F15" s="36"/>
+      <c r="G15" s="36"/>
       <c r="H15" s="23"/>
     </row>
-    <row r="16" spans="1:9" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:9" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B16" s="11"/>
-      <c r="C16" s="43"/>
-      <c r="D16" s="43"/>
-      <c r="E16" s="44" t="s">
+      <c r="E16" s="17" t="s">
         <v>4</v>
       </c>
-      <c r="F16" s="45"/>
-      <c r="G16" s="44" t="s">
+      <c r="G16" s="17" t="s">
         <v>5</v>
       </c>
       <c r="H16" s="13"/>
@@ -1198,10 +1209,10 @@
       <c r="C17" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="46"/>
-      <c r="E17" s="47"/>
+      <c r="D17" s="28"/>
+      <c r="E17" s="29"/>
       <c r="F17" s="24"/>
-      <c r="G17" s="47"/>
+      <c r="G17" s="29"/>
       <c r="H17" s="13"/>
     </row>
     <row r="18" spans="2:8" ht="12" customHeight="1" x14ac:dyDescent="0.25">
@@ -1213,22 +1224,22 @@
     </row>
     <row r="19" spans="2:8" ht="99" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B19" s="11"/>
-      <c r="C19" s="52" t="s">
+      <c r="C19" s="37" t="s">
         <v>6</v>
       </c>
-      <c r="D19" s="53"/>
-      <c r="E19" s="53"/>
-      <c r="F19" s="53"/>
-      <c r="G19" s="54"/>
+      <c r="D19" s="38"/>
+      <c r="E19" s="38"/>
+      <c r="F19" s="38"/>
+      <c r="G19" s="39"/>
       <c r="H19" s="13"/>
     </row>
     <row r="20" spans="2:8" ht="12" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B20" s="26"/>
-      <c r="C20" s="30"/>
-      <c r="D20" s="30"/>
-      <c r="E20" s="30"/>
-      <c r="F20" s="30"/>
-      <c r="G20" s="30"/>
+      <c r="C20" s="35"/>
+      <c r="D20" s="35"/>
+      <c r="E20" s="35"/>
+      <c r="F20" s="35"/>
+      <c r="G20" s="35"/>
       <c r="H20" s="27"/>
     </row>
   </sheetData>

--- a/owlcms/src/main/resources/templates/credentials/Athletes_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Athletes_A4.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40B06AED-3D01-4E4C-BBAD-29BAC89AF153}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78510AA1-ECB7-4B7B-8080-00F45577FA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6735" yWindow="3555" windowWidth="19620" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -88,7 +88,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t xml:space="preserve">jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="300" lastCell="G12")
+          <t xml:space="preserve">jx:image(src="local.getBytes('pictures/'+athlete.membership+'.jpg')" imageType="JPEG" ptHeight="260" lastCell="G12")
 </t>
         </r>
       </text>
@@ -210,7 +210,7 @@
     <t>${a.custom1} ${a.custom2}</t>
   </si>
   <si>
-    <t>ATHLETE</t>
+    <t>${t.get("Athlete")}</t>
   </si>
 </sst>
 </file>

--- a/owlcms/src/main/resources/templates/credentials/Athletes_A4.xlsx
+++ b/owlcms/src/main/resources/templates/credentials/Athletes_A4.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29231"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Dev\git\owlcms_v23\owlcms\src\main\resources\templates\credentials\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\lamyj\git\owlcms4\owlcms\src\main\resources\templates\credentials\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{78510AA1-ECB7-4B7B-8080-00F45577FA0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9994AA84-8427-4EC4-9303-A7007D741B7E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6735" yWindow="3555" windowWidth="19620" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191028" iterateDelta="1E-4"/>
+  <calcPr calcId="191028"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -168,7 +168,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>jx:image(src="local.getBytes('logos/liveQR.png')" imageType="PNG" ptHeight="100" lastCell="G19")</t>
+          <t>jx:image(src="local.getBytes('logos/sponsors.png')" imageType="PNG" ptHeight="100" lastCell="G19")</t>
         </r>
       </text>
     </comment>
